--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H285"/>
+  <dimension ref="A1:H286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8314,6 +8314,34 @@
         <v>1238.692</v>
       </c>
     </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>831</v>
+      </c>
+      <c r="C286" t="n">
+        <v>679</v>
+      </c>
+      <c r="D286" t="n">
+        <v>831</v>
+      </c>
+      <c r="E286" t="n">
+        <v>813</v>
+      </c>
+      <c r="F286" t="n">
+        <v>816</v>
+      </c>
+      <c r="G286" t="n">
+        <v>1139.419</v>
+      </c>
+      <c r="H286" t="n">
+        <v>1288.092</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H286"/>
+  <dimension ref="A1:H287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8342,6 +8342,34 @@
         <v>1288.092</v>
       </c>
     </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>828</v>
+      </c>
+      <c r="C287" t="n">
+        <v>672</v>
+      </c>
+      <c r="D287" t="n">
+        <v>825</v>
+      </c>
+      <c r="E287" t="n">
+        <v>805</v>
+      </c>
+      <c r="F287" t="n">
+        <v>814</v>
+      </c>
+      <c r="G287" t="n">
+        <v>1140.372</v>
+      </c>
+      <c r="H287" t="n">
+        <v>1289.028</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H287"/>
+  <dimension ref="A1:H288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8370,6 +8370,34 @@
         <v>1289.028</v>
       </c>
     </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>808</v>
+      </c>
+      <c r="C288" t="n">
+        <v>659</v>
+      </c>
+      <c r="D288" t="n">
+        <v>806</v>
+      </c>
+      <c r="E288" t="n">
+        <v>775</v>
+      </c>
+      <c r="F288" t="n">
+        <v>798</v>
+      </c>
+      <c r="G288" t="n">
+        <v>1144.186</v>
+      </c>
+      <c r="H288" t="n">
+        <v>1309.152</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H288"/>
+  <dimension ref="A1:H289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8398,6 +8398,34 @@
         <v>1309.152</v>
       </c>
     </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>762</v>
+      </c>
+      <c r="C289" t="n">
+        <v>640</v>
+      </c>
+      <c r="D289" t="n">
+        <v>774</v>
+      </c>
+      <c r="E289" t="n">
+        <v>761</v>
+      </c>
+      <c r="F289" t="n">
+        <v>765</v>
+      </c>
+      <c r="G289" t="n">
+        <v>1132.744</v>
+      </c>
+      <c r="H289" t="n">
+        <v>1254.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H289"/>
+  <dimension ref="A1:H290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8426,6 +8426,34 @@
         <v>1254.5</v>
       </c>
     </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>775</v>
+      </c>
+      <c r="C290" t="n">
+        <v>643</v>
+      </c>
+      <c r="D290" t="n">
+        <v>782</v>
+      </c>
+      <c r="E290" t="n">
+        <v>770</v>
+      </c>
+      <c r="F290" t="n">
+        <v>772</v>
+      </c>
+      <c r="G290" t="n">
+        <v>1132.744</v>
+      </c>
+      <c r="H290" t="n">
+        <v>1283.776</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H290"/>
+  <dimension ref="A1:H291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8454,6 +8454,34 @@
         <v>1283.776</v>
       </c>
     </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>791</v>
+      </c>
+      <c r="C291" t="n">
+        <v>660</v>
+      </c>
+      <c r="D291" t="n">
+        <v>793</v>
+      </c>
+      <c r="E291" t="n">
+        <v>780</v>
+      </c>
+      <c r="F291" t="n">
+        <v>785</v>
+      </c>
+      <c r="G291" t="n">
+        <v>1132.744</v>
+      </c>
+      <c r="H291" t="n">
+        <v>1331.616</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H291"/>
+  <dimension ref="A1:H292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8482,6 +8482,32 @@
         <v>1331.616</v>
       </c>
     </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>822</v>
+      </c>
+      <c r="C292" t="inlineStr"/>
+      <c r="D292" t="n">
+        <v>824</v>
+      </c>
+      <c r="E292" t="n">
+        <v>811</v>
+      </c>
+      <c r="F292" t="n">
+        <v>805</v>
+      </c>
+      <c r="G292" t="n">
+        <v>1148</v>
+      </c>
+      <c r="H292" t="n">
+        <v>1337.128</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H292"/>
+  <dimension ref="A1:H293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8508,6 +8508,34 @@
         <v>1337.128</v>
       </c>
     </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>844</v>
+      </c>
+      <c r="C293" t="n">
+        <v>682</v>
+      </c>
+      <c r="D293" t="n">
+        <v>848</v>
+      </c>
+      <c r="E293" t="n">
+        <v>836</v>
+      </c>
+      <c r="F293" t="n">
+        <v>820</v>
+      </c>
+      <c r="G293" t="n">
+        <v>1157.535</v>
+      </c>
+      <c r="H293" t="n">
+        <v>1360.58</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H293"/>
+  <dimension ref="A1:H294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8536,6 +8536,34 @@
         <v>1360.58</v>
       </c>
     </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>843</v>
+      </c>
+      <c r="C294" t="n">
+        <v>674</v>
+      </c>
+      <c r="D294" t="n">
+        <v>861</v>
+      </c>
+      <c r="E294" t="n">
+        <v>846</v>
+      </c>
+      <c r="F294" t="n">
+        <v>825</v>
+      </c>
+      <c r="G294" t="n">
+        <v>1161.349</v>
+      </c>
+      <c r="H294" t="n">
+        <v>1380.496</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H294"/>
+  <dimension ref="A1:H295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8539,28 +8539,56 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>855</v>
+      </c>
+      <c r="C294" t="n">
+        <v>680</v>
+      </c>
+      <c r="D294" t="n">
+        <v>864</v>
+      </c>
+      <c r="E294" t="n">
+        <v>853</v>
+      </c>
+      <c r="F294" t="n">
+        <v>835</v>
+      </c>
+      <c r="G294" t="n">
+        <v>1167.07</v>
+      </c>
+      <c r="H294" t="n">
+        <v>1399.216</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B294" t="n">
+      <c r="B295" t="n">
         <v>843</v>
       </c>
-      <c r="C294" t="n">
+      <c r="C295" t="n">
         <v>674</v>
       </c>
-      <c r="D294" t="n">
+      <c r="D295" t="n">
         <v>861</v>
       </c>
-      <c r="E294" t="n">
+      <c r="E295" t="n">
         <v>846</v>
       </c>
-      <c r="F294" t="n">
+      <c r="F295" t="n">
         <v>825</v>
       </c>
-      <c r="G294" t="n">
+      <c r="G295" t="n">
         <v>1161.349</v>
       </c>
-      <c r="H294" t="n">
+      <c r="H295" t="n">
         <v>1380.496</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H295"/>
+  <dimension ref="A1:H296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8592,6 +8592,34 @@
         <v>1380.496</v>
       </c>
     </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>833</v>
+      </c>
+      <c r="C296" t="n">
+        <v>684</v>
+      </c>
+      <c r="D296" t="n">
+        <v>850</v>
+      </c>
+      <c r="E296" t="n">
+        <v>832</v>
+      </c>
+      <c r="F296" t="n">
+        <v>818</v>
+      </c>
+      <c r="G296" t="n">
+        <v>1165.163</v>
+      </c>
+      <c r="H296" t="n">
+        <v>1376.596</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H296"/>
+  <dimension ref="A1:H297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8620,6 +8620,34 @@
         <v>1376.596</v>
       </c>
     </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>855</v>
+      </c>
+      <c r="C297" t="n">
+        <v>712</v>
+      </c>
+      <c r="D297" t="n">
+        <v>882</v>
+      </c>
+      <c r="E297" t="n">
+        <v>867</v>
+      </c>
+      <c r="F297" t="n">
+        <v>842</v>
+      </c>
+      <c r="G297" t="n">
+        <v>1205.209</v>
+      </c>
+      <c r="H297" t="n">
+        <v>1545.024</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H297"/>
+  <dimension ref="A1:H298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8623,28 +8623,56 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>844</v>
+      </c>
+      <c r="C297" t="n">
+        <v>698</v>
+      </c>
+      <c r="D297" t="n">
+        <v>874</v>
+      </c>
+      <c r="E297" t="n">
+        <v>844</v>
+      </c>
+      <c r="F297" t="n">
+        <v>840</v>
+      </c>
+      <c r="G297" t="n">
+        <v>1199.488</v>
+      </c>
+      <c r="H297" t="n">
+        <v>1529.06</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="B297" t="n">
+      <c r="B298" t="n">
         <v>855</v>
       </c>
-      <c r="C297" t="n">
+      <c r="C298" t="n">
         <v>712</v>
       </c>
-      <c r="D297" t="n">
+      <c r="D298" t="n">
         <v>882</v>
       </c>
-      <c r="E297" t="n">
+      <c r="E298" t="n">
         <v>867</v>
       </c>
-      <c r="F297" t="n">
+      <c r="F298" t="n">
         <v>842</v>
       </c>
-      <c r="G297" t="n">
+      <c r="G298" t="n">
         <v>1205.209</v>
       </c>
-      <c r="H297" t="n">
+      <c r="H298" t="n">
         <v>1545.024</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H298"/>
+  <dimension ref="A1:H299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8623,56 +8623,84 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B297" t="n">
-        <v>844</v>
+        <v>852</v>
       </c>
       <c r="C297" t="n">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="D297" t="n">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="E297" t="n">
-        <v>844</v>
+        <v>829</v>
       </c>
       <c r="F297" t="n">
         <v>840</v>
       </c>
       <c r="G297" t="n">
-        <v>1199.488</v>
+        <v>1176.605</v>
       </c>
       <c r="H297" t="n">
-        <v>1529.06</v>
+        <v>1446.952</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>844</v>
+      </c>
+      <c r="C298" t="n">
+        <v>698</v>
+      </c>
+      <c r="D298" t="n">
+        <v>874</v>
+      </c>
+      <c r="E298" t="n">
+        <v>844</v>
+      </c>
+      <c r="F298" t="n">
+        <v>840</v>
+      </c>
+      <c r="G298" t="n">
+        <v>1199.488</v>
+      </c>
+      <c r="H298" t="n">
+        <v>1529.06</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="B298" t="n">
+      <c r="B299" t="n">
         <v>855</v>
       </c>
-      <c r="C298" t="n">
+      <c r="C299" t="n">
         <v>712</v>
       </c>
-      <c r="D298" t="n">
+      <c r="D299" t="n">
         <v>882</v>
       </c>
-      <c r="E298" t="n">
+      <c r="E299" t="n">
         <v>867</v>
       </c>
-      <c r="F298" t="n">
+      <c r="F299" t="n">
         <v>842</v>
       </c>
-      <c r="G298" t="n">
+      <c r="G299" t="n">
         <v>1205.209</v>
       </c>
-      <c r="H298" t="n">
+      <c r="H299" t="n">
         <v>1545.024</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H299"/>
+  <dimension ref="A1:H300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8623,84 +8623,110 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B297" t="n">
-        <v>852</v>
+        <v>832</v>
       </c>
       <c r="C297" t="n">
-        <v>695</v>
+        <v>677</v>
       </c>
       <c r="D297" t="n">
-        <v>875</v>
-      </c>
-      <c r="E297" t="n">
-        <v>829</v>
-      </c>
+        <v>855</v>
+      </c>
+      <c r="E297" t="inlineStr"/>
       <c r="F297" t="n">
-        <v>840</v>
+        <v>825</v>
       </c>
       <c r="G297" t="n">
         <v>1176.605</v>
       </c>
       <c r="H297" t="n">
-        <v>1446.952</v>
+        <v>1410.396</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B298" t="n">
-        <v>844</v>
+        <v>852</v>
       </c>
       <c r="C298" t="n">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="D298" t="n">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="E298" t="n">
-        <v>844</v>
+        <v>829</v>
       </c>
       <c r="F298" t="n">
         <v>840</v>
       </c>
       <c r="G298" t="n">
-        <v>1199.488</v>
+        <v>1176.605</v>
       </c>
       <c r="H298" t="n">
-        <v>1529.06</v>
+        <v>1446.952</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>844</v>
+      </c>
+      <c r="C299" t="n">
+        <v>698</v>
+      </c>
+      <c r="D299" t="n">
+        <v>874</v>
+      </c>
+      <c r="E299" t="n">
+        <v>844</v>
+      </c>
+      <c r="F299" t="n">
+        <v>840</v>
+      </c>
+      <c r="G299" t="n">
+        <v>1199.488</v>
+      </c>
+      <c r="H299" t="n">
+        <v>1529.06</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="B299" t="n">
+      <c r="B300" t="n">
         <v>855</v>
       </c>
-      <c r="C299" t="n">
+      <c r="C300" t="n">
         <v>712</v>
       </c>
-      <c r="D299" t="n">
+      <c r="D300" t="n">
         <v>882</v>
       </c>
-      <c r="E299" t="n">
+      <c r="E300" t="n">
         <v>867</v>
       </c>
-      <c r="F299" t="n">
+      <c r="F300" t="n">
         <v>842</v>
       </c>
-      <c r="G299" t="n">
+      <c r="G300" t="n">
         <v>1205.209</v>
       </c>
-      <c r="H299" t="n">
+      <c r="H300" t="n">
         <v>1545.024</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H300"/>
+  <dimension ref="A1:H301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8730,6 +8730,34 @@
         <v>1545.024</v>
       </c>
     </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>890</v>
+      </c>
+      <c r="C301" t="n">
+        <v>710</v>
+      </c>
+      <c r="D301" t="n">
+        <v>902</v>
+      </c>
+      <c r="E301" t="n">
+        <v>866</v>
+      </c>
+      <c r="F301" t="n">
+        <v>870</v>
+      </c>
+      <c r="G301" t="n">
+        <v>1214.744</v>
+      </c>
+      <c r="H301" t="n">
+        <v>1536.704</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H301"/>
+  <dimension ref="A1:H302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8758,6 +8758,34 @@
         <v>1536.704</v>
       </c>
     </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>890</v>
+      </c>
+      <c r="C302" t="n">
+        <v>732</v>
+      </c>
+      <c r="D302" t="n">
+        <v>905</v>
+      </c>
+      <c r="E302" t="n">
+        <v>885</v>
+      </c>
+      <c r="F302" t="n">
+        <v>893</v>
+      </c>
+      <c r="G302" t="n">
+        <v>1218.558</v>
+      </c>
+      <c r="H302" t="n">
+        <v>1587.82</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H302"/>
+  <dimension ref="A1:H303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8786,6 +8786,34 @@
         <v>1587.82</v>
       </c>
     </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>900</v>
+      </c>
+      <c r="C303" t="n">
+        <v>706</v>
+      </c>
+      <c r="D303" t="n">
+        <v>905</v>
+      </c>
+      <c r="E303" t="n">
+        <v>870</v>
+      </c>
+      <c r="F303" t="n">
+        <v>910</v>
+      </c>
+      <c r="G303" t="n">
+        <v>1306.279</v>
+      </c>
+      <c r="H303" t="n">
+        <v>1471.288</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H303"/>
+  <dimension ref="A1:H304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8789,28 +8789,56 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>907</v>
+      </c>
+      <c r="C303" t="n">
+        <v>725</v>
+      </c>
+      <c r="D303" t="n">
+        <v>915</v>
+      </c>
+      <c r="E303" t="n">
+        <v>895</v>
+      </c>
+      <c r="F303" t="n">
+        <v>900</v>
+      </c>
+      <c r="G303" t="n">
+        <v>1254.791</v>
+      </c>
+      <c r="H303" t="n">
+        <v>1546.74</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="B303" t="n">
+      <c r="B304" t="n">
         <v>900</v>
       </c>
-      <c r="C303" t="n">
+      <c r="C304" t="n">
         <v>706</v>
       </c>
-      <c r="D303" t="n">
+      <c r="D304" t="n">
         <v>905</v>
       </c>
-      <c r="E303" t="n">
+      <c r="E304" t="n">
         <v>870</v>
       </c>
-      <c r="F303" t="n">
+      <c r="F304" t="n">
         <v>910</v>
       </c>
-      <c r="G303" t="n">
+      <c r="G304" t="n">
         <v>1306.279</v>
       </c>
-      <c r="H303" t="n">
+      <c r="H304" t="n">
         <v>1471.288</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H304"/>
+  <dimension ref="A1:H305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8817,28 +8817,56 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>916</v>
+      </c>
+      <c r="C304" t="n">
+        <v>713</v>
+      </c>
+      <c r="D304" t="n">
+        <v>925</v>
+      </c>
+      <c r="E304" t="n">
+        <v>900</v>
+      </c>
+      <c r="F304" t="n">
+        <v>915</v>
+      </c>
+      <c r="G304" t="n">
+        <v>1283.395</v>
+      </c>
+      <c r="H304" t="n">
+        <v>1492.556</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="B304" t="n">
+      <c r="B305" t="n">
         <v>900</v>
       </c>
-      <c r="C304" t="n">
+      <c r="C305" t="n">
         <v>706</v>
       </c>
-      <c r="D304" t="n">
+      <c r="D305" t="n">
         <v>905</v>
       </c>
-      <c r="E304" t="n">
+      <c r="E305" t="n">
         <v>870</v>
       </c>
-      <c r="F304" t="n">
+      <c r="F305" t="n">
         <v>910</v>
       </c>
-      <c r="G304" t="n">
+      <c r="G305" t="n">
         <v>1306.279</v>
       </c>
-      <c r="H304" t="n">
+      <c r="H305" t="n">
         <v>1471.288</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H305"/>
+  <dimension ref="A1:H306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8870,6 +8870,34 @@
         <v>1471.288</v>
       </c>
     </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>870</v>
+      </c>
+      <c r="C306" t="n">
+        <v>705</v>
+      </c>
+      <c r="D306" t="n">
+        <v>889</v>
+      </c>
+      <c r="E306" t="n">
+        <v>862</v>
+      </c>
+      <c r="F306" t="n">
+        <v>890</v>
+      </c>
+      <c r="G306" t="n">
+        <v>1312.953</v>
+      </c>
+      <c r="H306" t="n">
+        <v>1460.264</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H306"/>
+  <dimension ref="A1:H307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8898,6 +8898,34 @@
         <v>1460.264</v>
       </c>
     </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>848</v>
+      </c>
+      <c r="C307" t="n">
+        <v>675</v>
+      </c>
+      <c r="D307" t="n">
+        <v>884</v>
+      </c>
+      <c r="E307" t="n">
+        <v>845</v>
+      </c>
+      <c r="F307" t="n">
+        <v>915</v>
+      </c>
+      <c r="G307" t="n">
+        <v>1312.953</v>
+      </c>
+      <c r="H307" t="n">
+        <v>1457.144</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H307"/>
+  <dimension ref="A1:H308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8926,6 +8926,34 @@
         <v>1457.144</v>
       </c>
     </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>850</v>
+      </c>
+      <c r="C308" t="n">
+        <v>685</v>
+      </c>
+      <c r="D308" t="n">
+        <v>878</v>
+      </c>
+      <c r="E308" t="n">
+        <v>839</v>
+      </c>
+      <c r="F308" t="n">
+        <v>950</v>
+      </c>
+      <c r="G308" t="n">
+        <v>1312.953</v>
+      </c>
+      <c r="H308" t="n">
+        <v>1403.48</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H308"/>
+  <dimension ref="A1:H309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8929,28 +8929,56 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B308" t="n">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C308" t="n">
-        <v>685</v>
+        <v>665</v>
       </c>
       <c r="D308" t="n">
-        <v>878</v>
+        <v>888</v>
       </c>
       <c r="E308" t="n">
-        <v>839</v>
+        <v>829</v>
       </c>
       <c r="F308" t="n">
-        <v>950</v>
+        <v>945</v>
       </c>
       <c r="G308" t="n">
         <v>1312.953</v>
       </c>
       <c r="H308" t="n">
+        <v>1413.412</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>850</v>
+      </c>
+      <c r="C309" t="n">
+        <v>685</v>
+      </c>
+      <c r="D309" t="n">
+        <v>878</v>
+      </c>
+      <c r="E309" t="n">
+        <v>839</v>
+      </c>
+      <c r="F309" t="n">
+        <v>950</v>
+      </c>
+      <c r="G309" t="n">
+        <v>1312.953</v>
+      </c>
+      <c r="H309" t="n">
         <v>1403.48</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H309"/>
+  <dimension ref="A1:H310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8982,6 +8982,34 @@
         <v>1403.48</v>
       </c>
     </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>879</v>
+      </c>
+      <c r="C310" t="n">
+        <v>706</v>
+      </c>
+      <c r="D310" t="n">
+        <v>898</v>
+      </c>
+      <c r="E310" t="n">
+        <v>853</v>
+      </c>
+      <c r="F310" t="n">
+        <v>1020</v>
+      </c>
+      <c r="G310" t="n">
+        <v>1315.814</v>
+      </c>
+      <c r="H310" t="n">
+        <v>1425.528</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H310"/>
+  <dimension ref="A1:H311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9010,6 +9010,34 @@
         <v>1425.528</v>
       </c>
     </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>865</v>
+      </c>
+      <c r="C311" t="n">
+        <v>689</v>
+      </c>
+      <c r="D311" t="n">
+        <v>919</v>
+      </c>
+      <c r="E311" t="n">
+        <v>843</v>
+      </c>
+      <c r="F311" t="n">
+        <v>980</v>
+      </c>
+      <c r="G311" t="n">
+        <v>1315.814</v>
+      </c>
+      <c r="H311" t="n">
+        <v>1392.924</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H311"/>
+  <dimension ref="A1:H312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9038,6 +9038,34 @@
         <v>1392.924</v>
       </c>
     </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>865</v>
+      </c>
+      <c r="C312" t="n">
+        <v>698</v>
+      </c>
+      <c r="D312" t="n">
+        <v>919</v>
+      </c>
+      <c r="E312" t="n">
+        <v>837</v>
+      </c>
+      <c r="F312" t="n">
+        <v>970</v>
+      </c>
+      <c r="G312" t="n">
+        <v>1367.302</v>
+      </c>
+      <c r="H312" t="n">
+        <v>1416.324</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H312"/>
+  <dimension ref="A1:H313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9066,6 +9066,34 @@
         <v>1416.324</v>
       </c>
     </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>848</v>
+      </c>
+      <c r="C313" t="n">
+        <v>680</v>
+      </c>
+      <c r="D313" t="n">
+        <v>911</v>
+      </c>
+      <c r="E313" t="n">
+        <v>825</v>
+      </c>
+      <c r="F313" t="n">
+        <v>915</v>
+      </c>
+      <c r="G313" t="n">
+        <v>1367.302</v>
+      </c>
+      <c r="H313" t="n">
+        <v>1330.628</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H313"/>
+  <dimension ref="A1:H314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9069,28 +9069,56 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B313" t="n">
-        <v>848</v>
+        <v>855</v>
       </c>
       <c r="C313" t="n">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="D313" t="n">
-        <v>911</v>
+        <v>919</v>
       </c>
       <c r="E313" t="n">
-        <v>825</v>
+        <v>812</v>
       </c>
       <c r="F313" t="n">
-        <v>915</v>
+        <v>938</v>
       </c>
       <c r="G313" t="n">
         <v>1367.302</v>
       </c>
       <c r="H313" t="n">
+        <v>1376.96</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>848</v>
+      </c>
+      <c r="C314" t="n">
+        <v>680</v>
+      </c>
+      <c r="D314" t="n">
+        <v>911</v>
+      </c>
+      <c r="E314" t="n">
+        <v>825</v>
+      </c>
+      <c r="F314" t="n">
+        <v>915</v>
+      </c>
+      <c r="G314" t="n">
+        <v>1367.302</v>
+      </c>
+      <c r="H314" t="n">
         <v>1330.628</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H314"/>
+  <dimension ref="A1:H315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9122,6 +9122,34 @@
         <v>1330.628</v>
       </c>
     </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>886</v>
+      </c>
+      <c r="C315" t="n">
+        <v>685</v>
+      </c>
+      <c r="D315" t="n">
+        <v>930</v>
+      </c>
+      <c r="E315" t="n">
+        <v>858</v>
+      </c>
+      <c r="F315" t="n">
+        <v>938</v>
+      </c>
+      <c r="G315" t="n">
+        <v>1367.302</v>
+      </c>
+      <c r="H315" t="n">
+        <v>1387.36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H315"/>
+  <dimension ref="A1:H316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9150,6 +9150,34 @@
         <v>1387.36</v>
       </c>
     </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>880</v>
+      </c>
+      <c r="C316" t="n">
+        <v>674</v>
+      </c>
+      <c r="D316" t="n">
+        <v>919</v>
+      </c>
+      <c r="E316" t="n">
+        <v>844</v>
+      </c>
+      <c r="F316" t="n">
+        <v>928</v>
+      </c>
+      <c r="G316" t="n">
+        <v>1367.302</v>
+      </c>
+      <c r="H316" t="n">
+        <v>1350.388</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H316"/>
+  <dimension ref="A1:H317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9178,6 +9178,34 @@
         <v>1350.388</v>
       </c>
     </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>890</v>
+      </c>
+      <c r="C317" t="n">
+        <v>683</v>
+      </c>
+      <c r="D317" t="n">
+        <v>934</v>
+      </c>
+      <c r="E317" t="n">
+        <v>871</v>
+      </c>
+      <c r="F317" t="n">
+        <v>933</v>
+      </c>
+      <c r="G317" t="n">
+        <v>1367.302</v>
+      </c>
+      <c r="H317" t="n">
+        <v>1381.588</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H317"/>
+  <dimension ref="A1:H318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9206,6 +9206,34 @@
         <v>1381.588</v>
       </c>
     </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>899</v>
+      </c>
+      <c r="C318" t="n">
+        <v>665</v>
+      </c>
+      <c r="D318" t="n">
+        <v>943</v>
+      </c>
+      <c r="E318" t="n">
+        <v>870</v>
+      </c>
+      <c r="F318" t="n">
+        <v>928</v>
+      </c>
+      <c r="G318" t="n">
+        <v>1367.302</v>
+      </c>
+      <c r="H318" t="n">
+        <v>1412.268</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H318"/>
+  <dimension ref="A1:H319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9234,6 +9234,34 @@
         <v>1412.268</v>
       </c>
     </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>892</v>
+      </c>
+      <c r="C319" t="n">
+        <v>720</v>
+      </c>
+      <c r="D319" t="n">
+        <v>938</v>
+      </c>
+      <c r="E319" t="n">
+        <v>862</v>
+      </c>
+      <c r="F319" t="n">
+        <v>915</v>
+      </c>
+      <c r="G319" t="n">
+        <v>1367.302</v>
+      </c>
+      <c r="H319" t="n">
+        <v>1435.044</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H319"/>
+  <dimension ref="A1:H320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9237,28 +9237,56 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B319" t="n">
-        <v>892</v>
+        <v>897</v>
       </c>
       <c r="C319" t="n">
-        <v>720</v>
+        <v>695</v>
       </c>
       <c r="D319" t="n">
-        <v>938</v>
+        <v>943</v>
       </c>
       <c r="E319" t="n">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="F319" t="n">
-        <v>915</v>
+        <v>920</v>
       </c>
       <c r="G319" t="n">
         <v>1367.302</v>
       </c>
       <c r="H319" t="n">
+        <v>1392.092</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>892</v>
+      </c>
+      <c r="C320" t="n">
+        <v>720</v>
+      </c>
+      <c r="D320" t="n">
+        <v>938</v>
+      </c>
+      <c r="E320" t="n">
+        <v>862</v>
+      </c>
+      <c r="F320" t="n">
+        <v>915</v>
+      </c>
+      <c r="G320" t="n">
+        <v>1367.302</v>
+      </c>
+      <c r="H320" t="n">
         <v>1435.044</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H320"/>
+  <dimension ref="A1:H321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9290,6 +9290,34 @@
         <v>1435.044</v>
       </c>
     </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>881</v>
+      </c>
+      <c r="C321" t="n">
+        <v>733</v>
+      </c>
+      <c r="D321" t="n">
+        <v>936</v>
+      </c>
+      <c r="E321" t="n">
+        <v>872</v>
+      </c>
+      <c r="F321" t="n">
+        <v>913</v>
+      </c>
+      <c r="G321" t="n">
+        <v>1367.302</v>
+      </c>
+      <c r="H321" t="n">
+        <v>1416.584</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H321"/>
+  <dimension ref="A1:H322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9318,6 +9318,34 @@
         <v>1416.584</v>
       </c>
     </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>898</v>
+      </c>
+      <c r="C322" t="n">
+        <v>750</v>
+      </c>
+      <c r="D322" t="n">
+        <v>938</v>
+      </c>
+      <c r="E322" t="n">
+        <v>878</v>
+      </c>
+      <c r="F322" t="n">
+        <v>925</v>
+      </c>
+      <c r="G322" t="n">
+        <v>1367.302</v>
+      </c>
+      <c r="H322" t="n">
+        <v>1503.268</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H322"/>
+  <dimension ref="A1:H323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9346,6 +9346,34 @@
         <v>1503.268</v>
       </c>
     </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>917</v>
+      </c>
+      <c r="C323" t="n">
+        <v>720</v>
+      </c>
+      <c r="D323" t="n">
+        <v>940</v>
+      </c>
+      <c r="E323" t="n">
+        <v>881</v>
+      </c>
+      <c r="F323" t="n">
+        <v>937</v>
+      </c>
+      <c r="G323" t="n">
+        <v>1367.302</v>
+      </c>
+      <c r="H323" t="n">
+        <v>1569.724</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H323"/>
+  <dimension ref="A1:H324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9374,6 +9374,34 @@
         <v>1569.724</v>
       </c>
     </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>905</v>
+      </c>
+      <c r="C324" t="n">
+        <v>730</v>
+      </c>
+      <c r="D324" t="n">
+        <v>930</v>
+      </c>
+      <c r="E324" t="n">
+        <v>875</v>
+      </c>
+      <c r="F324" t="n">
+        <v>920</v>
+      </c>
+      <c r="G324" t="n">
+        <v>1367.302</v>
+      </c>
+      <c r="H324" t="n">
+        <v>1568.528</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H324"/>
+  <dimension ref="A1:H325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9377,28 +9377,56 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B324" t="n">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="C324" t="n">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="D324" t="n">
-        <v>930</v>
+        <v>946</v>
       </c>
       <c r="E324" t="n">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="F324" t="n">
-        <v>920</v>
+        <v>926</v>
       </c>
       <c r="G324" t="n">
         <v>1367.302</v>
       </c>
       <c r="H324" t="n">
+        <v>1563.484</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>905</v>
+      </c>
+      <c r="C325" t="n">
+        <v>730</v>
+      </c>
+      <c r="D325" t="n">
+        <v>930</v>
+      </c>
+      <c r="E325" t="n">
+        <v>875</v>
+      </c>
+      <c r="F325" t="n">
+        <v>920</v>
+      </c>
+      <c r="G325" t="n">
+        <v>1367.302</v>
+      </c>
+      <c r="H325" t="n">
         <v>1568.528</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H325"/>
+  <dimension ref="A1:H326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9430,6 +9430,34 @@
         <v>1568.528</v>
       </c>
     </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>910</v>
+      </c>
+      <c r="C326" t="n">
+        <v>740</v>
+      </c>
+      <c r="D326" t="n">
+        <v>935</v>
+      </c>
+      <c r="E326" t="n">
+        <v>878</v>
+      </c>
+      <c r="F326" t="n">
+        <v>926</v>
+      </c>
+      <c r="G326" t="n">
+        <v>1367.302</v>
+      </c>
+      <c r="H326" t="n">
+        <v>1592.864</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H326"/>
+  <dimension ref="A1:H327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9458,6 +9458,34 @@
         <v>1592.864</v>
       </c>
     </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>933</v>
+      </c>
+      <c r="C327" t="n">
+        <v>765</v>
+      </c>
+      <c r="D327" t="n">
+        <v>953</v>
+      </c>
+      <c r="E327" t="n">
+        <v>898</v>
+      </c>
+      <c r="F327" t="n">
+        <v>945</v>
+      </c>
+      <c r="G327" t="n">
+        <v>1357.767</v>
+      </c>
+      <c r="H327" t="n">
+        <v>1618.552</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H327"/>
+  <dimension ref="A1:H328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9486,6 +9486,34 @@
         <v>1618.552</v>
       </c>
     </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>960</v>
+      </c>
+      <c r="C328" t="n">
+        <v>768</v>
+      </c>
+      <c r="D328" t="n">
+        <v>960</v>
+      </c>
+      <c r="E328" t="n">
+        <v>898</v>
+      </c>
+      <c r="F328" t="n">
+        <v>940</v>
+      </c>
+      <c r="G328" t="n">
+        <v>1357.767</v>
+      </c>
+      <c r="H328" t="n">
+        <v>1625.572</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H328"/>
+  <dimension ref="A1:H329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9489,28 +9489,56 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B328" t="n">
-        <v>960</v>
+        <v>933</v>
       </c>
       <c r="C328" t="n">
-        <v>768</v>
+        <v>753</v>
       </c>
       <c r="D328" t="n">
-        <v>960</v>
+        <v>935</v>
       </c>
       <c r="E328" t="n">
-        <v>898</v>
+        <v>878</v>
       </c>
       <c r="F328" t="n">
-        <v>940</v>
+        <v>925</v>
       </c>
       <c r="G328" t="n">
         <v>1357.767</v>
       </c>
       <c r="H328" t="n">
+        <v>1614.08</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>960</v>
+      </c>
+      <c r="C329" t="n">
+        <v>768</v>
+      </c>
+      <c r="D329" t="n">
+        <v>960</v>
+      </c>
+      <c r="E329" t="n">
+        <v>898</v>
+      </c>
+      <c r="F329" t="n">
+        <v>940</v>
+      </c>
+      <c r="G329" t="n">
+        <v>1357.767</v>
+      </c>
+      <c r="H329" t="n">
         <v>1625.572</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H329"/>
+  <dimension ref="A1:H330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9461,84 +9461,112 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B327" t="n">
-        <v>933</v>
+        <v>915</v>
       </c>
       <c r="C327" t="n">
-        <v>765</v>
+        <v>745</v>
       </c>
       <c r="D327" t="n">
-        <v>953</v>
+        <v>938</v>
       </c>
       <c r="E327" t="n">
-        <v>898</v>
+        <v>888</v>
       </c>
       <c r="F327" t="n">
-        <v>945</v>
+        <v>930</v>
       </c>
       <c r="G327" t="n">
-        <v>1357.767</v>
+        <v>1367.302</v>
       </c>
       <c r="H327" t="n">
-        <v>1618.552</v>
+        <v>1624.064</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B328" t="n">
         <v>933</v>
       </c>
       <c r="C328" t="n">
-        <v>753</v>
+        <v>765</v>
       </c>
       <c r="D328" t="n">
-        <v>935</v>
+        <v>953</v>
       </c>
       <c r="E328" t="n">
-        <v>878</v>
+        <v>898</v>
       </c>
       <c r="F328" t="n">
-        <v>925</v>
+        <v>945</v>
       </c>
       <c r="G328" t="n">
         <v>1357.767</v>
       </c>
       <c r="H328" t="n">
-        <v>1614.08</v>
+        <v>1618.552</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B329" t="n">
-        <v>960</v>
+        <v>933</v>
       </c>
       <c r="C329" t="n">
-        <v>768</v>
+        <v>753</v>
       </c>
       <c r="D329" t="n">
-        <v>960</v>
+        <v>935</v>
       </c>
       <c r="E329" t="n">
-        <v>898</v>
+        <v>878</v>
       </c>
       <c r="F329" t="n">
-        <v>940</v>
+        <v>925</v>
       </c>
       <c r="G329" t="n">
         <v>1357.767</v>
       </c>
       <c r="H329" t="n">
+        <v>1614.08</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>960</v>
+      </c>
+      <c r="C330" t="n">
+        <v>768</v>
+      </c>
+      <c r="D330" t="n">
+        <v>960</v>
+      </c>
+      <c r="E330" t="n">
+        <v>898</v>
+      </c>
+      <c r="F330" t="n">
+        <v>940</v>
+      </c>
+      <c r="G330" t="n">
+        <v>1357.767</v>
+      </c>
+      <c r="H330" t="n">
         <v>1625.572</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H330"/>
+  <dimension ref="A1:H331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9570,6 +9570,34 @@
         <v>1625.572</v>
       </c>
     </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>980</v>
+      </c>
+      <c r="C331" t="n">
+        <v>779</v>
+      </c>
+      <c r="D331" t="n">
+        <v>977</v>
+      </c>
+      <c r="E331" t="n">
+        <v>917</v>
+      </c>
+      <c r="F331" t="n">
+        <v>953</v>
+      </c>
+      <c r="G331" t="n">
+        <v>1357.767</v>
+      </c>
+      <c r="H331" t="n">
+        <v>1681.212</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H331"/>
+  <dimension ref="A1:H332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9598,6 +9598,34 @@
         <v>1681.212</v>
       </c>
     </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>1018</v>
+      </c>
+      <c r="C332" t="n">
+        <v>765</v>
+      </c>
+      <c r="D332" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E332" t="n">
+        <v>948</v>
+      </c>
+      <c r="F332" t="n">
+        <v>970</v>
+      </c>
+      <c r="G332" t="n">
+        <v>1357.767</v>
+      </c>
+      <c r="H332" t="n">
+        <v>1719.016</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H332"/>
+  <dimension ref="A1:H333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9601,28 +9601,56 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B332" t="n">
-        <v>1018</v>
+        <v>1005</v>
       </c>
       <c r="C332" t="n">
-        <v>765</v>
+        <v>730</v>
       </c>
       <c r="D332" t="n">
-        <v>1000</v>
+        <v>984</v>
       </c>
       <c r="E332" t="n">
-        <v>948</v>
+        <v>924</v>
       </c>
       <c r="F332" t="n">
-        <v>970</v>
+        <v>963</v>
       </c>
       <c r="G332" t="n">
         <v>1357.767</v>
       </c>
       <c r="H332" t="n">
+        <v>1715.272</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>1018</v>
+      </c>
+      <c r="C333" t="n">
+        <v>765</v>
+      </c>
+      <c r="D333" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E333" t="n">
+        <v>948</v>
+      </c>
+      <c r="F333" t="n">
+        <v>970</v>
+      </c>
+      <c r="G333" t="n">
+        <v>1357.767</v>
+      </c>
+      <c r="H333" t="n">
         <v>1719.016</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H333"/>
+  <dimension ref="A1:H334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9601,56 +9601,84 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B332" t="n">
-        <v>1005</v>
+        <v>990</v>
       </c>
       <c r="C332" t="n">
-        <v>730</v>
+        <v>770</v>
       </c>
       <c r="D332" t="n">
-        <v>984</v>
+        <v>979</v>
       </c>
       <c r="E332" t="n">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="F332" t="n">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="G332" t="n">
         <v>1357.767</v>
       </c>
       <c r="H332" t="n">
-        <v>1715.272</v>
+        <v>1737.996</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B333" t="n">
-        <v>1018</v>
+        <v>1005</v>
       </c>
       <c r="C333" t="n">
-        <v>765</v>
+        <v>730</v>
       </c>
       <c r="D333" t="n">
-        <v>1000</v>
+        <v>984</v>
       </c>
       <c r="E333" t="n">
-        <v>948</v>
+        <v>924</v>
       </c>
       <c r="F333" t="n">
-        <v>970</v>
+        <v>963</v>
       </c>
       <c r="G333" t="n">
         <v>1357.767</v>
       </c>
       <c r="H333" t="n">
+        <v>1715.272</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>1018</v>
+      </c>
+      <c r="C334" t="n">
+        <v>765</v>
+      </c>
+      <c r="D334" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E334" t="n">
+        <v>948</v>
+      </c>
+      <c r="F334" t="n">
+        <v>970</v>
+      </c>
+      <c r="G334" t="n">
+        <v>1357.767</v>
+      </c>
+      <c r="H334" t="n">
         <v>1719.016</v>
       </c>
     </row>

--- a/history_data/extracted_data.xlsx
+++ b/history_data/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H334"/>
+  <dimension ref="A1:H335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9682,6 +9682,34 @@
         <v>1719.016</v>
       </c>
     </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
+        <v>1018</v>
+      </c>
+      <c r="C335" t="n">
+        <v>760</v>
+      </c>
+      <c r="D335" t="n">
+        <v>1001</v>
+      </c>
+      <c r="E335" t="n">
+        <v>947</v>
+      </c>
+      <c r="F335" t="n">
+        <v>968</v>
+      </c>
+      <c r="G335" t="n">
+        <v>1357.767</v>
+      </c>
+      <c r="H335" t="n">
+        <v>1699.828</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
